--- a/app/reports/TMC_research.xlsx
+++ b/app/reports/TMC_research.xlsx
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-26 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/TMC_research.xlsx
+++ b/app/reports/TMC_research.xlsx
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-27 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3.93</v>
+        <v>3.784</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.05184000015258789</v>
+        <v>0.05293000221252441</v>
       </c>
     </row>
     <row r="6">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>565836930.2798982</v>
+        <v>565836921.7758986</v>
       </c>
     </row>
     <row r="36">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>3.93</v>
+        <v>3.784</v>
       </c>
     </row>
     <row r="38">
@@ -1481,11 +1481,11 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>2223739136</v>
+        <v>2141126912</v>
       </c>
       <c r="D5" s="29" t="n"/>
       <c r="E5" s="29" t="n">
-        <v>-7.95</v>
+        <v>-7.8</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>2691518976</v>
+        <v>2635867136</v>
       </c>
       <c r="D6" s="31" t="n">
-        <v>26.149153</v>
+        <v>25.608473</v>
       </c>
       <c r="E6" s="31" t="n">
-        <v>9.124000000000001</v>
+        <v>9.065</v>
       </c>
       <c r="F6" s="31" t="n">
-        <v>0.455</v>
+        <v>0.452</v>
       </c>
     </row>
     <row r="7">
@@ -1525,16 +1525,16 @@
         </is>
       </c>
       <c r="C7" s="30" t="n">
-        <v>3459741696</v>
+        <v>3322121728</v>
       </c>
       <c r="D7" s="31" t="n">
-        <v>9.823528</v>
+        <v>9.432772999999999</v>
       </c>
       <c r="E7" s="31" t="n">
-        <v>4.173</v>
+        <v>3.983</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>2.648</v>
+        <v>2.528</v>
       </c>
     </row>
     <row r="8">
@@ -1549,16 +1549,16 @@
         </is>
       </c>
       <c r="C8" s="30" t="n">
-        <v>4553273856</v>
+        <v>4633345536</v>
       </c>
       <c r="D8" s="31" t="n">
-        <v>66.880684</v>
+        <v>68.056816</v>
       </c>
       <c r="E8" s="31" t="n">
-        <v>6.812</v>
+        <v>6.877</v>
       </c>
       <c r="F8" s="31" t="n">
-        <v>1.785</v>
+        <v>1.802</v>
       </c>
     </row>
     <row r="9">
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="C9" s="30" t="n">
-        <v>5520103424</v>
+        <v>5590938112</v>
       </c>
       <c r="D9" s="31" t="n">
-        <v>61.762238</v>
+        <v>62.409298</v>
       </c>
       <c r="E9" s="31" t="n">
-        <v>29.257</v>
+        <v>28.955</v>
       </c>
       <c r="F9" s="31" t="n">
-        <v>2.865</v>
+        <v>2.835</v>
       </c>
     </row>
     <row r="10">
@@ -1597,11 +1597,11 @@
         </is>
       </c>
       <c r="C10" s="30" t="n">
-        <v>3978422272</v>
+        <v>3724987648</v>
       </c>
       <c r="D10" s="31" t="n"/>
       <c r="E10" s="31" t="n">
-        <v>-65.10899999999999</v>
+        <v>-62.074</v>
       </c>
       <c r="F10" s="31" t="n"/>
     </row>
@@ -1617,16 +1617,16 @@
         </is>
       </c>
       <c r="C11" s="30" t="n">
-        <v>1572281984</v>
+        <v>1525255552</v>
       </c>
       <c r="D11" s="31" t="n">
-        <v>12.435087</v>
+        <v>12.063159</v>
       </c>
       <c r="E11" s="31" t="n">
-        <v>7.653</v>
+        <v>7.493</v>
       </c>
       <c r="F11" s="31" t="n">
-        <v>1.631</v>
+        <v>1.597</v>
       </c>
     </row>
     <row r="12">
@@ -1641,16 +1641,16 @@
         </is>
       </c>
       <c r="C12" s="30" t="n">
-        <v>2553570816</v>
+        <v>2509321216</v>
       </c>
       <c r="D12" s="31" t="n">
-        <v>14.427084</v>
+        <v>14.177083</v>
       </c>
       <c r="E12" s="31" t="n">
-        <v>8.57</v>
+        <v>8.523999999999999</v>
       </c>
       <c r="F12" s="31" t="n">
-        <v>1.789</v>
+        <v>1.779</v>
       </c>
     </row>
     <row r="13">
@@ -1665,14 +1665,14 @@
         </is>
       </c>
       <c r="C13" s="30" t="n">
-        <v>5698461696</v>
+        <v>5272391168</v>
       </c>
       <c r="D13" s="31" t="n"/>
       <c r="E13" s="31" t="n">
-        <v>-20.429</v>
+        <v>-18.688</v>
       </c>
       <c r="F13" s="31" t="n">
-        <v>166.934</v>
+        <v>152.711</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/TMC_research.xlsx
+++ b/app/reports/TMC_research.xlsx
@@ -617,7 +617,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-09-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>3.784</v>
+        <v>3.915</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>0.05293000221252441</v>
+        <v>0.05302000045776367</v>
       </c>
     </row>
     <row r="6">
@@ -1181,7 +1181,7 @@
         </is>
       </c>
       <c r="B35" s="18" t="n">
-        <v>565836921.7758986</v>
+        <v>565836898.0842912</v>
       </c>
     </row>
     <row r="36">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="B37" s="20" t="n">
-        <v>3.784</v>
+        <v>3.915</v>
       </c>
     </row>
     <row r="38">
@@ -1481,11 +1481,11 @@
         </is>
       </c>
       <c r="C5" s="28" t="n">
-        <v>2141126912</v>
+        <v>2215251456</v>
       </c>
       <c r="D5" s="29" t="n"/>
       <c r="E5" s="29" t="n">
-        <v>-7.8</v>
+        <v>-7.55</v>
       </c>
       <c r="F5" s="29" t="n"/>
     </row>
@@ -1501,16 +1501,16 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>2635867136</v>
+        <v>2621387264</v>
       </c>
       <c r="D6" s="31" t="n">
-        <v>25.608473</v>
+        <v>25.467794</v>
       </c>
       <c r="E6" s="31" t="n">
-        <v>9.065</v>
+        <v>8.997</v>
       </c>
       <c r="F6" s="31" t="n">
-        <v>0.452</v>
+        <v>0.448</v>
       </c>
     </row>
     <row r="7">
@@ -1525,16 +1525,16 @@
         </is>
       </c>
       <c r="C7" s="30" t="n">
-        <v>3322121728</v>
+        <v>3333959936</v>
       </c>
       <c r="D7" s="31" t="n">
-        <v>9.432772999999999</v>
+        <v>9.466386999999999</v>
       </c>
       <c r="E7" s="31" t="n">
-        <v>3.983</v>
+        <v>4.039</v>
       </c>
       <c r="F7" s="31" t="n">
-        <v>2.528</v>
+        <v>2.563</v>
       </c>
     </row>
     <row r="8">
@@ -1549,16 +1549,16 @@
         </is>
       </c>
       <c r="C8" s="30" t="n">
-        <v>4633345536</v>
+        <v>4579964416</v>
       </c>
       <c r="D8" s="31" t="n">
-        <v>68.056816</v>
+        <v>67.27273</v>
       </c>
       <c r="E8" s="31" t="n">
-        <v>6.877</v>
+        <v>6.854</v>
       </c>
       <c r="F8" s="31" t="n">
-        <v>1.802</v>
+        <v>1.796</v>
       </c>
     </row>
     <row r="9">
@@ -1573,16 +1573,16 @@
         </is>
       </c>
       <c r="C9" s="30" t="n">
-        <v>5590938112</v>
+        <v>5640939520</v>
       </c>
       <c r="D9" s="31" t="n">
-        <v>62.409298</v>
+        <v>62.96744</v>
       </c>
       <c r="E9" s="31" t="n">
-        <v>28.955</v>
+        <v>29.622</v>
       </c>
       <c r="F9" s="31" t="n">
-        <v>2.835</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -1597,11 +1597,11 @@
         </is>
       </c>
       <c r="C10" s="30" t="n">
-        <v>3724987648</v>
+        <v>3760744704</v>
       </c>
       <c r="D10" s="31" t="n"/>
       <c r="E10" s="31" t="n">
-        <v>-62.074</v>
+        <v>-62.585</v>
       </c>
       <c r="F10" s="31" t="n"/>
     </row>
@@ -1617,16 +1617,16 @@
         </is>
       </c>
       <c r="C11" s="30" t="n">
-        <v>1525255552</v>
+        <v>1571172864</v>
       </c>
       <c r="D11" s="31" t="n">
-        <v>12.063159</v>
+        <v>12.426316</v>
       </c>
       <c r="E11" s="31" t="n">
-        <v>7.493</v>
+        <v>7.516</v>
       </c>
       <c r="F11" s="31" t="n">
-        <v>1.597</v>
+        <v>1.602</v>
       </c>
     </row>
     <row r="12">
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="C12" s="30" t="n">
-        <v>2509321216</v>
+        <v>2537899264</v>
       </c>
       <c r="D12" s="31" t="n">
-        <v>14.177083</v>
+        <v>14.338542</v>
       </c>
       <c r="E12" s="31" t="n">
         <v>8.523999999999999</v>
@@ -1665,14 +1665,14 @@
         </is>
       </c>
       <c r="C13" s="30" t="n">
-        <v>5272391168</v>
+        <v>5403778560</v>
       </c>
       <c r="D13" s="31" t="n"/>
       <c r="E13" s="31" t="n">
-        <v>-18.688</v>
+        <v>-17.915</v>
       </c>
       <c r="F13" s="31" t="n">
-        <v>152.711</v>
+        <v>146.389</v>
       </c>
     </row>
     <row r="15">
